--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/74.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/74.xlsx
@@ -426,13 +426,13 @@
         <v>-6.034416597459055</v>
       </c>
       <c r="E2">
-        <v>-4.071584756322074</v>
+        <v>-2.96997458379416</v>
       </c>
       <c r="F2">
-        <v>-3.629315480356745</v>
+        <v>-2.905464849503259</v>
       </c>
       <c r="G2">
-        <v>-8.544306396654076</v>
+        <v>-7.381871316011154</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.712523099473199</v>
       </c>
       <c r="E3">
-        <v>-3.31893426235123</v>
+        <v>-4.67037581740831</v>
       </c>
       <c r="F3">
-        <v>-3.775690485533626</v>
+        <v>-2.537695402049765</v>
       </c>
       <c r="G3">
-        <v>-8.627669111593328</v>
+        <v>-6.535024124955627</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.543022786536786</v>
       </c>
       <c r="E4">
-        <v>-4.754542035314872</v>
+        <v>-5.125718407353572</v>
       </c>
       <c r="F4">
-        <v>-3.588312950652975</v>
+        <v>-2.525767739816855</v>
       </c>
       <c r="G4">
-        <v>-8.578447506980098</v>
+        <v>-6.905575756885279</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.522537340005481</v>
       </c>
       <c r="E5">
-        <v>-5.719577960245455</v>
+        <v>-4.604889554783389</v>
       </c>
       <c r="F5">
-        <v>-3.746715022151102</v>
+        <v>-2.439227368878988</v>
       </c>
       <c r="G5">
-        <v>-7.703539309148199</v>
+        <v>-6.607115843838187</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.564843794996827</v>
       </c>
       <c r="E6">
-        <v>-5.288086842898593</v>
+        <v>-5.934041960774715</v>
       </c>
       <c r="F6">
-        <v>-3.633894695359421</v>
+        <v>-3.00309954506682</v>
       </c>
       <c r="G6">
-        <v>-8.013545840862976</v>
+        <v>-6.76817788530509</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.600062666035007</v>
       </c>
       <c r="E7">
-        <v>-6.536351646164912</v>
+        <v>-6.336872366127032</v>
       </c>
       <c r="F7">
-        <v>-3.739511539216358</v>
+        <v>-2.857333389930997</v>
       </c>
       <c r="G7">
-        <v>-7.988336215621762</v>
+        <v>-5.325989135725473</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.564125994813466</v>
       </c>
       <c r="E8">
-        <v>-7.013621107255314</v>
+        <v>-7.278686276346282</v>
       </c>
       <c r="F8">
-        <v>-3.794052905751483</v>
+        <v>-2.297961733842574</v>
       </c>
       <c r="G8">
-        <v>-7.443315470933316</v>
+        <v>-6.497906946675188</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.419893006415822</v>
       </c>
       <c r="E9">
-        <v>-7.704516801183557</v>
+        <v>-7.594067320136477</v>
       </c>
       <c r="F9">
-        <v>-3.811738549801253</v>
+        <v>-3.05879648412885</v>
       </c>
       <c r="G9">
-        <v>-6.916945189588755</v>
+        <v>-5.817742529617894</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.153112076298474</v>
       </c>
       <c r="E10">
-        <v>-7.778829059649428</v>
+        <v>-8.132665904712759</v>
       </c>
       <c r="F10">
-        <v>-3.740477415608022</v>
+        <v>-2.5811730935531</v>
       </c>
       <c r="G10">
-        <v>-6.366326680919896</v>
+        <v>-3.97614052327175</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.772621557742121</v>
       </c>
       <c r="E11">
-        <v>-7.751563117649244</v>
+        <v>-8.869059176996066</v>
       </c>
       <c r="F11">
-        <v>-3.80220404099503</v>
+        <v>-2.866544835450127</v>
       </c>
       <c r="G11">
-        <v>-6.186341834719675</v>
+        <v>-4.541268593676473</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.300800100211763</v>
       </c>
       <c r="E12">
-        <v>-8.542375062082726</v>
+        <v>-9.228959648755668</v>
       </c>
       <c r="F12">
-        <v>-3.345665085922736</v>
+        <v>-2.604610920847909</v>
       </c>
       <c r="G12">
-        <v>-5.139999654071469</v>
+        <v>-4.058614027168392</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.771646597519956</v>
       </c>
       <c r="E13">
-        <v>-9.851982574256947</v>
+        <v>-11.01828652645844</v>
       </c>
       <c r="F13">
-        <v>-3.630155444903184</v>
+        <v>-2.649628547353049</v>
       </c>
       <c r="G13">
-        <v>-4.458338999983066</v>
+        <v>-3.1594411959044</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.231549383401265</v>
       </c>
       <c r="E14">
-        <v>-10.32341483235146</v>
+        <v>-11.12156290467737</v>
       </c>
       <c r="F14">
-        <v>-3.858130437827636</v>
+        <v>-2.638793501724431</v>
       </c>
       <c r="G14">
-        <v>-4.489097170881301</v>
+        <v>-1.875079203334074</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.733031886660576</v>
       </c>
       <c r="E15">
-        <v>-10.41894752001728</v>
+        <v>-11.35733337541272</v>
       </c>
       <c r="F15">
-        <v>-3.532541458524693</v>
+        <v>-2.528984290441926</v>
       </c>
       <c r="G15">
-        <v>-3.252424452455945</v>
+        <v>-2.022793235497157</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.333099172378946</v>
       </c>
       <c r="E16">
-        <v>-11.7250137655175</v>
+        <v>-12.56002814473985</v>
       </c>
       <c r="F16">
-        <v>-3.406941079442621</v>
+        <v>-2.177025063238263</v>
       </c>
       <c r="G16">
-        <v>-2.489816062496042</v>
+        <v>-1.039877067593016</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.08347300303963</v>
       </c>
       <c r="E17">
-        <v>-12.37676080164943</v>
+        <v>-12.36921636395265</v>
       </c>
       <c r="F17">
-        <v>-3.261363792074636</v>
+        <v>-1.163675764087003</v>
       </c>
       <c r="G17">
-        <v>-2.111028564452184</v>
+        <v>-1.062205780305038</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.02246220385584</v>
       </c>
       <c r="E18">
-        <v>-13.06216798508038</v>
+        <v>-14.51986565425344</v>
       </c>
       <c r="F18">
-        <v>-2.855141529783189</v>
+        <v>-1.23015141979426</v>
       </c>
       <c r="G18">
-        <v>-1.906152371502016</v>
+        <v>-1.376723991664051</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.16297879525212</v>
       </c>
       <c r="E19">
-        <v>-13.05973619453826</v>
+        <v>-14.41773045148444</v>
       </c>
       <c r="F19">
-        <v>-2.52141052727813</v>
+        <v>-0.7808731050075037</v>
       </c>
       <c r="G19">
-        <v>-1.405208276021591</v>
+        <v>-1.475482198160219</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.494435241028793</v>
       </c>
       <c r="E20">
-        <v>-14.11564953585477</v>
+        <v>-16.58375391104126</v>
       </c>
       <c r="F20">
-        <v>-1.986111227915061</v>
+        <v>-1.003137333057056</v>
       </c>
       <c r="G20">
-        <v>-1.52511067424682</v>
+        <v>-0.8800520466540238</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.981877083037318</v>
       </c>
       <c r="E21">
-        <v>-15.60103882358474</v>
+        <v>-16.25778982349514</v>
       </c>
       <c r="F21">
-        <v>-1.896107452866089</v>
+        <v>-0.45207337365131</v>
       </c>
       <c r="G21">
-        <v>-1.234591317373585</v>
+        <v>-1.29128426347767</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.571794338444852</v>
       </c>
       <c r="E22">
-        <v>-16.01212463705303</v>
+        <v>-15.95751124052053</v>
       </c>
       <c r="F22">
-        <v>-1.642159828394262</v>
+        <v>-0.4247952350771222</v>
       </c>
       <c r="G22">
-        <v>-1.667627251459742</v>
+        <v>-1.530242504765791</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.197590458988159</v>
       </c>
       <c r="E23">
-        <v>-16.47822235276652</v>
+        <v>-17.19882483618508</v>
       </c>
       <c r="F23">
-        <v>-1.342521943086222</v>
+        <v>0.1501919749214734</v>
       </c>
       <c r="G23">
-        <v>-1.192893553796161</v>
+        <v>-1.251020393721724</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.790422380863158</v>
       </c>
       <c r="E24">
-        <v>-16.51290593519126</v>
+        <v>-17.96506528065294</v>
       </c>
       <c r="F24">
-        <v>-1.297779334558812</v>
+        <v>0.02277498612506185</v>
       </c>
       <c r="G24">
-        <v>-2.105457050244247</v>
+        <v>-1.431146332449001</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.285870105314887</v>
       </c>
       <c r="E25">
-        <v>-17.57919853893335</v>
+        <v>-17.16497449297774</v>
       </c>
       <c r="F25">
-        <v>-0.8807120862299141</v>
+        <v>0.6654398129323771</v>
       </c>
       <c r="G25">
-        <v>-2.4803694256264</v>
+        <v>-1.405900613770634</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.629714170618236</v>
       </c>
       <c r="E26">
-        <v>-16.75470380483082</v>
+        <v>-18.3580054987725</v>
       </c>
       <c r="F26">
-        <v>-1.054453865293082</v>
+        <v>0.7444876007119228</v>
       </c>
       <c r="G26">
-        <v>-2.542722478920528</v>
+        <v>-1.997567204148146</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.782313912975609</v>
       </c>
       <c r="E27">
-        <v>-17.13084338438193</v>
+        <v>-17.91523395267253</v>
       </c>
       <c r="F27">
-        <v>-0.8727763265110948</v>
+        <v>0.387084342937062</v>
       </c>
       <c r="G27">
-        <v>-3.231598539218149</v>
+        <v>-2.603910698561053</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.721463710168901</v>
       </c>
       <c r="E28">
-        <v>-17.28555869885399</v>
+        <v>-19.00342172824171</v>
       </c>
       <c r="F28">
-        <v>-1.062848540553053</v>
+        <v>0.6788577081229235</v>
       </c>
       <c r="G28">
-        <v>-3.13391985461504</v>
+        <v>-2.24814425097826</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.446456067850455</v>
       </c>
       <c r="E29">
-        <v>-17.40235257198581</v>
+        <v>-17.76719360888778</v>
       </c>
       <c r="F29">
-        <v>-0.7825762283876595</v>
+        <v>0.5151342044292124</v>
       </c>
       <c r="G29">
-        <v>-3.339741039374328</v>
+        <v>-3.168418618091041</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.976472852069098</v>
       </c>
       <c r="E30">
-        <v>-16.25236018315995</v>
+        <v>-16.6259275894747</v>
       </c>
       <c r="F30">
-        <v>-0.8856682084008636</v>
+        <v>0.9466738596524205</v>
       </c>
       <c r="G30">
-        <v>-3.277355173864606</v>
+        <v>-3.251902738227993</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.346680759346343</v>
       </c>
       <c r="E31">
-        <v>-16.09203861786639</v>
+        <v>-18.42226907341535</v>
       </c>
       <c r="F31">
-        <v>-0.9908725252912064</v>
+        <v>0.4396069781115647</v>
       </c>
       <c r="G31">
-        <v>-3.395859771705511</v>
+        <v>-2.252380308011503</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.602018796368748</v>
       </c>
       <c r="E32">
-        <v>-15.81676626836214</v>
+        <v>-18.17325281620757</v>
       </c>
       <c r="F32">
-        <v>-0.7666160736379214</v>
+        <v>0.6304793950646268</v>
       </c>
       <c r="G32">
-        <v>-3.840609666758886</v>
+        <v>-2.985198487433208</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.795157263481377</v>
       </c>
       <c r="E33">
-        <v>-16.29126883183385</v>
+        <v>-16.86091916268073</v>
       </c>
       <c r="F33">
-        <v>-0.9286347972166711</v>
+        <v>0.6642171426458451</v>
       </c>
       <c r="G33">
-        <v>-4.633575918586772</v>
+        <v>-3.337939648738193</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.98197278629001</v>
       </c>
       <c r="E34">
-        <v>-16.32301343462762</v>
+        <v>-17.0910969680166</v>
       </c>
       <c r="F34">
-        <v>-0.841544390323345</v>
+        <v>0.6562673006811782</v>
       </c>
       <c r="G34">
-        <v>-4.067588168133474</v>
+        <v>-3.487878349118579</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.217368210637987</v>
       </c>
       <c r="E35">
-        <v>-15.43292828299799</v>
+        <v>-15.36523212505732</v>
       </c>
       <c r="F35">
-        <v>-0.7259912794698281</v>
+        <v>0.2906052199004064</v>
       </c>
       <c r="G35">
-        <v>-3.884541942218291</v>
+        <v>-3.278073761386124</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.5511333060442213</v>
       </c>
       <c r="E36">
-        <v>-15.26697329603889</v>
+        <v>-17.08604319102405</v>
       </c>
       <c r="F36">
-        <v>-0.7961689091001966</v>
+        <v>0.6962691625623663</v>
       </c>
       <c r="G36">
-        <v>-3.625148253057949</v>
+        <v>-3.598271767264537</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.02421560102768518</v>
       </c>
       <c r="E37">
-        <v>-14.8267286384352</v>
+        <v>-16.19357606206638</v>
       </c>
       <c r="F37">
-        <v>-0.7802667400686545</v>
+        <v>0.8984479661962388</v>
       </c>
       <c r="G37">
-        <v>-3.871269401010337</v>
+        <v>-4.087262372603904</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.3365681901497678</v>
       </c>
       <c r="E38">
-        <v>-14.8793313925083</v>
+        <v>-15.49714657290076</v>
       </c>
       <c r="F38">
-        <v>-0.3746077676111114</v>
+        <v>0.7433610210441154</v>
       </c>
       <c r="G38">
-        <v>-4.008152120805692</v>
+        <v>-3.167969090737397</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.5194965270660524</v>
       </c>
       <c r="E39">
-        <v>-13.51824418781488</v>
+        <v>-16.12200805884916</v>
       </c>
       <c r="F39">
-        <v>-0.646738884941791</v>
+        <v>0.9503700350037119</v>
       </c>
       <c r="G39">
-        <v>-3.223992667643357</v>
+        <v>-3.216226016212151</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.5252668781498488</v>
       </c>
       <c r="E40">
-        <v>-13.53743133218538</v>
+        <v>-15.25850957811856</v>
       </c>
       <c r="F40">
-        <v>-0.4472547604692252</v>
+        <v>0.7373205659429014</v>
       </c>
       <c r="G40">
-        <v>-3.126999758346171</v>
+        <v>-4.105328778510207</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.3683679835984928</v>
       </c>
       <c r="E41">
-        <v>-13.22575005165946</v>
+        <v>-13.64558940538458</v>
       </c>
       <c r="F41">
-        <v>-0.5107955104683641</v>
+        <v>0.4957835418998159</v>
       </c>
       <c r="G41">
-        <v>-3.476610634283446</v>
+        <v>-2.443938022651886</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.07348044221509462</v>
       </c>
       <c r="E42">
-        <v>-13.70941371804869</v>
+        <v>-13.47942158014713</v>
       </c>
       <c r="F42">
-        <v>-0.5694754005478755</v>
+        <v>0.5269550072671614</v>
       </c>
       <c r="G42">
-        <v>-3.137394668246491</v>
+        <v>-3.532552180650419</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.3282972574679286</v>
       </c>
       <c r="E43">
-        <v>-12.6149041927648</v>
+        <v>-13.11027849293787</v>
       </c>
       <c r="F43">
-        <v>-0.5540487144055403</v>
+        <v>0.5491362012119237</v>
       </c>
       <c r="G43">
-        <v>-2.810319221979483</v>
+        <v>-2.479614744667728</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.8035203879509257</v>
       </c>
       <c r="E44">
-        <v>-12.01012196056642</v>
+        <v>-13.05612700075415</v>
       </c>
       <c r="F44">
-        <v>-0.5342333377631733</v>
+        <v>0.5461979820341939</v>
       </c>
       <c r="G44">
-        <v>-2.566517897669621</v>
+        <v>-1.721504909465824</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.317339361758931</v>
       </c>
       <c r="E45">
-        <v>-11.6593010791922</v>
+        <v>-12.93603639854474</v>
       </c>
       <c r="F45">
-        <v>-0.7725397289353407</v>
+        <v>0.656817336636637</v>
       </c>
       <c r="G45">
-        <v>-2.575603600167724</v>
+        <v>-1.984980438246116</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.841682855478392</v>
       </c>
       <c r="E46">
-        <v>-11.56774439170512</v>
+        <v>-11.65319216775585</v>
       </c>
       <c r="F46">
-        <v>-0.5734449371420907</v>
+        <v>0.6329644972730253</v>
       </c>
       <c r="G46">
-        <v>-2.489405909801111</v>
+        <v>-1.532860919570228</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.354908587414233</v>
       </c>
       <c r="E47">
-        <v>-11.48563410099804</v>
+        <v>-11.66646965354634</v>
       </c>
       <c r="F47">
-        <v>-0.5114623462276177</v>
+        <v>0.7542407985124842</v>
       </c>
       <c r="G47">
-        <v>-2.359879688742031</v>
+        <v>-2.318021145308195</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.840513595559915</v>
       </c>
       <c r="E48">
-        <v>-10.02064106019862</v>
+        <v>-12.23291382479578</v>
       </c>
       <c r="F48">
-        <v>-0.7149623958689555</v>
+        <v>0.2169724698329611</v>
       </c>
       <c r="G48">
-        <v>-2.397902484172877</v>
+        <v>-1.668893802981687</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.285812633842398</v>
       </c>
       <c r="E49">
-        <v>-10.42127515565722</v>
+        <v>-11.21988966080592</v>
       </c>
       <c r="F49">
-        <v>-0.7233703250073704</v>
+        <v>0.6184606124174087</v>
       </c>
       <c r="G49">
-        <v>-2.256665583368138</v>
+        <v>-0.9680445652136527</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.685527868294577</v>
       </c>
       <c r="E50">
-        <v>-10.1555895856272</v>
+        <v>-9.929641375014487</v>
       </c>
       <c r="F50">
-        <v>-0.6015920331218151</v>
+        <v>0.5040970371543118</v>
       </c>
       <c r="G50">
-        <v>-2.531786167462899</v>
+        <v>-1.113770177111711</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.035180358289916</v>
       </c>
       <c r="E51">
-        <v>-9.802699191631472</v>
+        <v>-9.954932902347325</v>
       </c>
       <c r="F51">
-        <v>-0.6577114395592732</v>
+        <v>0.443385990203136</v>
       </c>
       <c r="G51">
-        <v>-2.097624774381853</v>
+        <v>-1.455141905713221</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.330595991886991</v>
       </c>
       <c r="E52">
-        <v>-8.748927818520587</v>
+        <v>-9.686394393692474</v>
       </c>
       <c r="F52">
-        <v>-0.6903996456411445</v>
+        <v>0.6892520622932516</v>
       </c>
       <c r="G52">
-        <v>-1.784209053466812</v>
+        <v>-1.460683888927123</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.568289952211113</v>
       </c>
       <c r="E53">
-        <v>-8.534961950132169</v>
+        <v>-10.15130112074194</v>
       </c>
       <c r="F53">
-        <v>-0.7494390471734709</v>
+        <v>-0.1020732353552684</v>
       </c>
       <c r="G53">
-        <v>-2.135116011920068</v>
+        <v>-1.958832383638901</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.748920231785976</v>
       </c>
       <c r="E54">
-        <v>-8.537416383044327</v>
+        <v>-7.75975512712912</v>
       </c>
       <c r="F54">
-        <v>-0.7179138689251301</v>
+        <v>0.5104058832940328</v>
       </c>
       <c r="G54">
-        <v>-2.624372396205751</v>
+        <v>-2.198335307705889</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.8736781082706</v>
       </c>
       <c r="E55">
-        <v>-8.799918435846955</v>
+        <v>-9.063004661796572</v>
       </c>
       <c r="F55">
-        <v>-0.5377481006532516</v>
+        <v>0.1592236647141964</v>
       </c>
       <c r="G55">
-        <v>-2.572575032668357</v>
+        <v>-2.245532398616942</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.94458810030806</v>
       </c>
       <c r="E56">
-        <v>-7.66957962421438</v>
+        <v>-7.988352495036319</v>
       </c>
       <c r="F56">
-        <v>-0.5733090848880316</v>
+        <v>0.9189334920674707</v>
       </c>
       <c r="G56">
-        <v>-2.862861422810871</v>
+        <v>-2.385627434318994</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.964819586966064</v>
       </c>
       <c r="E57">
-        <v>-7.624743203064436</v>
+        <v>-8.758799891857308</v>
       </c>
       <c r="F57">
-        <v>-0.4881454605736172</v>
+        <v>0.3623766284137612</v>
       </c>
       <c r="G57">
-        <v>-3.5229742949184</v>
+        <v>-1.989141027183492</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.938736679229192</v>
       </c>
       <c r="E58">
-        <v>-6.406538410261033</v>
+        <v>-7.60916525247805</v>
       </c>
       <c r="F58">
-        <v>-0.2448440139625688</v>
+        <v>0.2138975700337694</v>
       </c>
       <c r="G58">
-        <v>-3.615773803062615</v>
+        <v>-2.795140291045492</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.873205324687606</v>
       </c>
       <c r="E59">
-        <v>-7.075307980187799</v>
+        <v>-7.361607163900734</v>
       </c>
       <c r="F59">
-        <v>-0.3735085240675964</v>
+        <v>0.8826841345209643</v>
       </c>
       <c r="G59">
-        <v>-3.248099802440597</v>
+        <v>-3.50045855257749</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.774602857444338</v>
       </c>
       <c r="E60">
-        <v>-7.45492089930279</v>
+        <v>-6.072323443072937</v>
       </c>
       <c r="F60">
-        <v>-0.3401501687568603</v>
+        <v>0.7238827899346878</v>
       </c>
       <c r="G60">
-        <v>-3.716061058805483</v>
+        <v>-3.023247532636529</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.648061842255736</v>
       </c>
       <c r="E61">
-        <v>-6.385639502715635</v>
+        <v>-6.046760207299639</v>
       </c>
       <c r="F61">
-        <v>-0.3064115928082393</v>
+        <v>0.5919230343013238</v>
       </c>
       <c r="G61">
-        <v>-3.563251289560583</v>
+        <v>-3.053917110552658</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.496311873484037</v>
       </c>
       <c r="E62">
-        <v>-6.685501466081543</v>
+        <v>-7.06482909133405</v>
       </c>
       <c r="F62">
-        <v>-0.1120434654153633</v>
+        <v>0.4995824348090545</v>
       </c>
       <c r="G62">
-        <v>-4.515465067332999</v>
+        <v>-3.68186744893451</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.32532806859457</v>
       </c>
       <c r="E63">
-        <v>-5.705349494913355</v>
+        <v>-6.02308081671353</v>
       </c>
       <c r="F63">
-        <v>-0.3948472683637117</v>
+        <v>0.702756936061092</v>
       </c>
       <c r="G63">
-        <v>-4.367570567984147</v>
+        <v>-4.260707744236152</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.14258047783878</v>
       </c>
       <c r="E64">
-        <v>-5.949275747336519</v>
+        <v>-6.095758296062632</v>
       </c>
       <c r="F64">
-        <v>-0.2455961715643108</v>
+        <v>0.5369086699792002</v>
       </c>
       <c r="G64">
-        <v>-4.776266400542344</v>
+        <v>-5.21238012045126</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.958719610213439</v>
       </c>
       <c r="E65">
-        <v>-5.861355424477598</v>
+        <v>-6.513039061973425</v>
       </c>
       <c r="F65">
-        <v>-0.1508483363995061</v>
+        <v>0.7334520901718277</v>
       </c>
       <c r="G65">
-        <v>-4.175199110397023</v>
+        <v>-4.874903201840811</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.785292535097696</v>
       </c>
       <c r="E66">
-        <v>-4.934666617443967</v>
+        <v>-6.602874929337589</v>
       </c>
       <c r="F66">
-        <v>-0.6580601822358518</v>
+        <v>0.771449302938241</v>
       </c>
       <c r="G66">
-        <v>-4.911771007282733</v>
+        <v>-4.356099417412329</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.634211455870254</v>
       </c>
       <c r="E67">
-        <v>-5.423755395694389</v>
+        <v>-6.961498371427028</v>
       </c>
       <c r="F67">
-        <v>-0.3040018720334955</v>
+        <v>0.7045851429190705</v>
       </c>
       <c r="G67">
-        <v>-4.492594953063669</v>
+        <v>-4.134423370077803</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.515698655931878</v>
       </c>
       <c r="E68">
-        <v>-5.580164359445315</v>
+        <v>-5.97994710179047</v>
       </c>
       <c r="F68">
-        <v>-0.2713376886063054</v>
+        <v>0.431313363674736</v>
       </c>
       <c r="G68">
-        <v>-4.465124566167998</v>
+        <v>-4.869768090100281</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.44032198012608</v>
       </c>
       <c r="E69">
-        <v>-4.878201075042326</v>
+        <v>-6.171229843874466</v>
       </c>
       <c r="F69">
-        <v>-0.534317002870856</v>
+        <v>0.6668745452740259</v>
       </c>
       <c r="G69">
-        <v>-5.409158258592718</v>
+        <v>-4.613215938810417</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.4183700762054</v>
       </c>
       <c r="E70">
-        <v>-5.7610497252077</v>
+        <v>-6.018230821051315</v>
       </c>
       <c r="F70">
-        <v>-0.5505347798828648</v>
+        <v>0.5122042689255105</v>
       </c>
       <c r="G70">
-        <v>-4.806066454745221</v>
+        <v>-4.629579390727367</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.456423517101295</v>
       </c>
       <c r="E71">
-        <v>-5.55449696876984</v>
+        <v>-6.322675600112985</v>
       </c>
       <c r="F71">
-        <v>-0.2933954558080507</v>
+        <v>0.4880855236256001</v>
       </c>
       <c r="G71">
-        <v>-5.029872014871826</v>
+        <v>-5.114832684710528</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.558662813779727</v>
       </c>
       <c r="E72">
-        <v>-5.877349994672691</v>
+        <v>-6.116870041886391</v>
       </c>
       <c r="F72">
-        <v>-0.6879957234382204</v>
+        <v>0.623500399696041</v>
       </c>
       <c r="G72">
-        <v>-5.027991874918264</v>
+        <v>-4.986097238047273</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.724170238008177</v>
       </c>
       <c r="E73">
-        <v>-5.485003006648131</v>
+        <v>-5.678916792130583</v>
       </c>
       <c r="F73">
-        <v>-0.6335860673201404</v>
+        <v>0.5032438187294282</v>
       </c>
       <c r="G73">
-        <v>-4.435206387988981</v>
+        <v>-5.119042491971295</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.949615017355835</v>
       </c>
       <c r="E74">
-        <v>-5.777805079036081</v>
+        <v>-6.568784577007847</v>
       </c>
       <c r="F74">
-        <v>-0.6088137401394212</v>
+        <v>0.5754260974745716</v>
       </c>
       <c r="G74">
-        <v>-4.807336287488726</v>
+        <v>-4.649877027294092</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.22555949244935</v>
       </c>
       <c r="E75">
-        <v>-6.695047489289712</v>
+        <v>-6.649450284506479</v>
       </c>
       <c r="F75">
-        <v>-0.7893224525160587</v>
+        <v>0.2496142873402757</v>
       </c>
       <c r="G75">
-        <v>-4.665430017485861</v>
+        <v>-4.026763209490863</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.54129542354694</v>
       </c>
       <c r="E76">
-        <v>-6.843336899144885</v>
+        <v>-6.25859769290445</v>
       </c>
       <c r="F76">
-        <v>-0.9562451111193815</v>
+        <v>0.2024122559939542</v>
       </c>
       <c r="G76">
-        <v>-4.429940027386073</v>
+        <v>-5.290630692200898</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.882659543259894</v>
       </c>
       <c r="E77">
-        <v>-7.235747285805552</v>
+        <v>-7.018960178110357</v>
       </c>
       <c r="F77">
-        <v>-0.7829142022880017</v>
+        <v>0.3916461622242789</v>
       </c>
       <c r="G77">
-        <v>-4.303314406185542</v>
+        <v>-3.831117092787412</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.234015380855905</v>
       </c>
       <c r="E78">
-        <v>-7.535518679691307</v>
+        <v>-7.643183149223669</v>
       </c>
       <c r="F78">
-        <v>-0.8201078986736995</v>
+        <v>-0.01287794689142887</v>
       </c>
       <c r="G78">
-        <v>-4.261127740595761</v>
+        <v>-4.880494403378105</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.576253047155551</v>
       </c>
       <c r="E79">
-        <v>-7.514329949809417</v>
+        <v>-7.90490177602297</v>
       </c>
       <c r="F79">
-        <v>-0.9083025193149573</v>
+        <v>0.03088553136587182</v>
       </c>
       <c r="G79">
-        <v>-4.382677312043831</v>
+        <v>-3.694637963243869</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.894062869734715</v>
       </c>
       <c r="E80">
-        <v>-8.371705933681646</v>
+        <v>-9.015256431859695</v>
       </c>
       <c r="F80">
-        <v>-1.222854331343</v>
+        <v>0.3923370206382137</v>
       </c>
       <c r="G80">
-        <v>-3.286207909631988</v>
+        <v>-3.584500480379547</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.172347361464901</v>
       </c>
       <c r="E81">
-        <v>-8.53076405472706</v>
+        <v>-8.025549380535324</v>
       </c>
       <c r="F81">
-        <v>-0.9223375482205893</v>
+        <v>-0.272677987064035</v>
       </c>
       <c r="G81">
-        <v>-4.025880560891372</v>
+        <v>-3.967035133444291</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.399181079318898</v>
       </c>
       <c r="E82">
-        <v>-9.817606928064722</v>
+        <v>-10.5599460867201</v>
       </c>
       <c r="F82">
-        <v>-0.9023473860562317</v>
+        <v>-0.3285124351149301</v>
       </c>
       <c r="G82">
-        <v>-3.618293781220268</v>
+        <v>-3.867623963857794</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.567071392565361</v>
       </c>
       <c r="E83">
-        <v>-10.51171783853841</v>
+        <v>-11.07520038778684</v>
       </c>
       <c r="F83">
-        <v>-1.030195125902099</v>
+        <v>0.0920662626344349</v>
       </c>
       <c r="G83">
-        <v>-3.847834916632783</v>
+        <v>-3.636494717210508</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.674988689334273</v>
       </c>
       <c r="E84">
-        <v>-11.85084647276864</v>
+        <v>-11.8204196559111</v>
       </c>
       <c r="F84">
-        <v>-1.098664661947895</v>
+        <v>-0.171829225977612</v>
       </c>
       <c r="G84">
-        <v>-3.525428648644864</v>
+        <v>-3.349758608795313</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.727362303378201</v>
       </c>
       <c r="E85">
-        <v>-13.05646663630472</v>
+        <v>-12.37344595867582</v>
       </c>
       <c r="F85">
-        <v>-1.530815652314369</v>
+        <v>-0.08424925394923147</v>
       </c>
       <c r="G85">
-        <v>-3.944535797211178</v>
+        <v>-3.857901704377159</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.731651976948745</v>
       </c>
       <c r="E86">
-        <v>-14.22723113540377</v>
+        <v>-14.53486396016684</v>
       </c>
       <c r="F86">
-        <v>-1.285837590080054</v>
+        <v>-0.457101563786303</v>
       </c>
       <c r="G86">
-        <v>-3.308051001553211</v>
+        <v>-3.700288226769232</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.700259384863854</v>
       </c>
       <c r="E87">
-        <v>-15.05687474445303</v>
+        <v>-16.1093373885757</v>
       </c>
       <c r="F87">
-        <v>-1.39576525790116</v>
+        <v>-0.1183788193119739</v>
       </c>
       <c r="G87">
-        <v>-2.877065830941707</v>
+        <v>-2.41472202588659</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.647302971101095</v>
       </c>
       <c r="E88">
-        <v>-17.38663423870519</v>
+        <v>-17.02872629550896</v>
       </c>
       <c r="F88">
-        <v>-1.6676776862375</v>
+        <v>-0.2292276316849925</v>
       </c>
       <c r="G88">
-        <v>-3.148931443249499</v>
+        <v>-2.958607467915468</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.588566909553331</v>
       </c>
       <c r="E89">
-        <v>-18.05552607743016</v>
+        <v>-18.79849922244661</v>
       </c>
       <c r="F89">
-        <v>-1.986794631022371</v>
+        <v>-0.1872178072194184</v>
       </c>
       <c r="G89">
-        <v>-2.850002315519407</v>
+        <v>-2.665450008908439</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.536409509531675</v>
       </c>
       <c r="E90">
-        <v>-19.74284002116215</v>
+        <v>-20.18555722557402</v>
       </c>
       <c r="F90">
-        <v>-1.771960030208527</v>
+        <v>-0.3393234580888664</v>
       </c>
       <c r="G90">
-        <v>-2.942585263040699</v>
+        <v>-3.057798795657482</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.504556705670046</v>
       </c>
       <c r="E91">
-        <v>-21.31933767745242</v>
+        <v>-21.27335102390453</v>
       </c>
       <c r="F91">
-        <v>-1.869768682926676</v>
+        <v>-0.7005082130575069</v>
       </c>
       <c r="G91">
-        <v>-2.925772283770105</v>
+        <v>-3.057729890004733</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.505130184666154</v>
       </c>
       <c r="E92">
-        <v>-24.28467302715513</v>
+        <v>-24.93283351187299</v>
       </c>
       <c r="F92">
-        <v>-1.845465211695942</v>
+        <v>-0.832649381152084</v>
       </c>
       <c r="G92">
-        <v>-2.471716844374145</v>
+        <v>-3.159073699089743</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.551653278358433</v>
       </c>
       <c r="E93">
-        <v>-25.69328656655905</v>
+        <v>-26.17449127156211</v>
       </c>
       <c r="F93">
-        <v>-2.114360725951286</v>
+        <v>-0.8778525619554503</v>
       </c>
       <c r="G93">
-        <v>-2.623204281330588</v>
+        <v>-2.553520979072661</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.654743968370056</v>
       </c>
       <c r="E94">
-        <v>-27.97335511552504</v>
+        <v>-28.61361794157352</v>
       </c>
       <c r="F94">
-        <v>-2.120298463494553</v>
+        <v>-1.126390947286997</v>
       </c>
       <c r="G94">
-        <v>-2.847419994152124</v>
+        <v>-2.894964894548478</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.82515597520505</v>
       </c>
       <c r="E95">
-        <v>-30.7358669071352</v>
+        <v>-31.38885248090823</v>
       </c>
       <c r="F95">
-        <v>-2.034190500340948</v>
+        <v>-0.8999625163035718</v>
       </c>
       <c r="G95">
-        <v>-2.837005396922446</v>
+        <v>-2.96604271596917</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.069050220302309</v>
       </c>
       <c r="E96">
-        <v>-32.98770268490038</v>
+        <v>-34.73436680897689</v>
       </c>
       <c r="F96">
-        <v>-2.429808831509157</v>
+        <v>-1.233184901223312</v>
       </c>
       <c r="G96">
-        <v>-3.310052546704473</v>
+        <v>-3.409306217656116</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.376307513187152</v>
       </c>
       <c r="E97">
-        <v>-35.64907100954922</v>
+        <v>-36.69806484258201</v>
       </c>
       <c r="F97">
-        <v>-2.683807814759959</v>
+        <v>-1.683846589572744</v>
       </c>
       <c r="G97">
-        <v>-3.197007901538483</v>
+        <v>-2.535241293764995</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.745176582451913</v>
       </c>
       <c r="E98">
-        <v>-38.3561610720165</v>
+        <v>-39.66225901683478</v>
       </c>
       <c r="F98">
-        <v>-2.732776753776452</v>
+        <v>-1.820709451863278</v>
       </c>
       <c r="G98">
-        <v>-3.718279164579668</v>
+        <v>-3.896380589604767</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.147814386583853</v>
       </c>
       <c r="E99">
-        <v>-40.81671874526921</v>
+        <v>-41.43497318764042</v>
       </c>
       <c r="F99">
-        <v>-2.833070508702999</v>
+        <v>-1.986972730013973</v>
       </c>
       <c r="G99">
-        <v>-3.609496826219397</v>
+        <v>-3.163539441632147</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.593882039454066</v>
       </c>
       <c r="E100">
-        <v>-43.48564735727386</v>
+        <v>-44.39417471929973</v>
       </c>
       <c r="F100">
-        <v>-3.322539553138782</v>
+        <v>-2.223180866554849</v>
       </c>
       <c r="G100">
-        <v>-4.083951620050425</v>
+        <v>-4.321023158941865</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.030433905644434</v>
       </c>
       <c r="E101">
-        <v>-45.6311387156799</v>
+        <v>-46.18054676771249</v>
       </c>
       <c r="F101">
-        <v>-3.068156207413082</v>
+        <v>-2.471401987171124</v>
       </c>
       <c r="G101">
-        <v>-4.370825539771117</v>
+        <v>-4.17787330596797</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.504758951875516</v>
       </c>
       <c r="E102">
-        <v>-48.88210529917941</v>
+        <v>-48.45820503638791</v>
       </c>
       <c r="F102">
-        <v>-3.247085223152581</v>
+        <v>-2.207156927515095</v>
       </c>
       <c r="G102">
-        <v>-4.416211396381356</v>
+        <v>-3.599777847960322</v>
       </c>
     </row>
   </sheetData>
